--- a/Sensitivity_Output/Top10_Configurations.xlsx
+++ b/Sensitivity_Output/Top10_Configurations.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>avg_distance_km</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
@@ -495,7 +507,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
@@ -507,22 +519,22 @@
         <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>27.42</v>
+        <v>24.43</v>
       </c>
       <c r="G2" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J2" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K2" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -541,7 +553,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
@@ -553,22 +565,22 @@
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>27.42</v>
+        <v>24.43</v>
       </c>
       <c r="G3" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J3" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K3" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -587,7 +599,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
@@ -599,22 +611,22 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>27.42</v>
+        <v>24.43</v>
       </c>
       <c r="G4" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J4" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K4" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -633,7 +645,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
@@ -645,22 +657,22 @@
         <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>27.42</v>
+        <v>24.43</v>
       </c>
       <c r="G5" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J5" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K5" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -679,7 +691,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
@@ -691,22 +703,22 @@
         <v>500</v>
       </c>
       <c r="F6" t="n">
-        <v>27.42</v>
+        <v>24.43</v>
       </c>
       <c r="G6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J6" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K6" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -721,11 +733,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
@@ -737,22 +749,22 @@
         <v>500</v>
       </c>
       <c r="F7" t="n">
-        <v>27.46</v>
+        <v>24.43</v>
       </c>
       <c r="G7" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>70.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J7" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K7" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -767,11 +779,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
@@ -783,22 +795,22 @@
         <v>500</v>
       </c>
       <c r="F8" t="n">
-        <v>27.46</v>
+        <v>24.43</v>
       </c>
       <c r="G8" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>70.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J8" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K8" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -813,11 +825,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
@@ -829,22 +841,22 @@
         <v>500</v>
       </c>
       <c r="F9" t="n">
-        <v>27.46</v>
+        <v>24.43</v>
       </c>
       <c r="G9" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>70.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J9" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K9" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -859,11 +871,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
@@ -875,22 +887,22 @@
         <v>500</v>
       </c>
       <c r="F10" t="n">
-        <v>27.46</v>
+        <v>24.43</v>
       </c>
       <c r="G10" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>70.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J10" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K10" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -905,11 +917,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
@@ -921,22 +933,22 @@
         <v>500</v>
       </c>
       <c r="F11" t="n">
-        <v>27.46</v>
+        <v>24.43</v>
       </c>
       <c r="G11" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>70.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J11" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K11" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Sensitivity_Output/Top10_Configurations.xlsx
+++ b/Sensitivity_Output/Top10_Configurations.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>avg_distance_km</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>avg_travel_hours</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
@@ -495,7 +507,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
@@ -507,22 +519,22 @@
         <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>27.42</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J2" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K2" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -541,7 +553,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
@@ -553,22 +565,22 @@
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>27.42</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J3" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K3" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -587,7 +599,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
@@ -599,22 +611,22 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>27.42</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J4" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K4" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -633,7 +645,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
@@ -645,22 +657,22 @@
         <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>27.42</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J5" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K5" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -679,7 +691,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
@@ -691,22 +703,22 @@
         <v>500</v>
       </c>
       <c r="F6" t="n">
-        <v>27.42</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J6" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K6" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -721,7 +733,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -737,22 +749,22 @@
         <v>500</v>
       </c>
       <c r="F7" t="n">
-        <v>27.46</v>
+        <v>1.18</v>
       </c>
       <c r="G7" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>70.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J7" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K7" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -767,7 +779,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -783,22 +795,22 @@
         <v>500</v>
       </c>
       <c r="F8" t="n">
-        <v>27.46</v>
+        <v>1.18</v>
       </c>
       <c r="G8" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>70.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J8" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K8" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -813,7 +825,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -829,22 +841,22 @@
         <v>500</v>
       </c>
       <c r="F9" t="n">
-        <v>27.46</v>
+        <v>1.18</v>
       </c>
       <c r="G9" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>70.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J9" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K9" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -859,7 +871,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -875,22 +887,22 @@
         <v>500</v>
       </c>
       <c r="F10" t="n">
-        <v>27.46</v>
+        <v>1.18</v>
       </c>
       <c r="G10" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>70.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J10" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K10" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -905,7 +917,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -921,22 +933,22 @@
         <v>500</v>
       </c>
       <c r="F11" t="n">
-        <v>27.46</v>
+        <v>1.18</v>
       </c>
       <c r="G11" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>70.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J11" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K11" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Sensitivity_Output/Top10_Configurations.xlsx
+++ b/Sensitivity_Output/Top10_Configurations.xlsx
@@ -503,11 +503,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>edd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
@@ -519,129 +519,129 @@
         <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K2" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>edd</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K3" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>edd</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>65.2</v>
+        <v>92.3</v>
       </c>
       <c r="J4" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="K4" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>edd</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -651,43 +651,43 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>65.2</v>
+        <v>92.3</v>
       </c>
       <c r="J5" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="K5" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>edd</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -697,135 +697,135 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>500</v>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>65.2</v>
+        <v>92.3</v>
       </c>
       <c r="J6" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="K6" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>edd</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
         <v>500</v>
       </c>
       <c r="F7" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>65.2</v>
+        <v>92.3</v>
       </c>
       <c r="J7" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="K7" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>edd</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
         <v>500</v>
       </c>
       <c r="F8" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>65.2</v>
+        <v>92.3</v>
       </c>
       <c r="J8" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="K8" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>edd</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -835,43 +835,43 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>500</v>
       </c>
       <c r="F9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="J9" t="n">
-        <v>65.2</v>
+        <v>92.3</v>
       </c>
       <c r="K9" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>edd</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -881,43 +881,43 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>500</v>
       </c>
       <c r="F10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="J10" t="n">
-        <v>65.2</v>
+        <v>92.3</v>
       </c>
       <c r="K10" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>edd</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -927,37 +927,37 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>500</v>
       </c>
       <c r="F11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="J11" t="n">
-        <v>65.2</v>
+        <v>92.3</v>
       </c>
       <c r="K11" t="n">
-        <v>65.2</v>
+        <v>92.8</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity_Output/Top10_Configurations.xlsx
+++ b/Sensitivity_Output/Top10_Configurations.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
@@ -519,31 +519,31 @@
         <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>1.02</v>
+        <v>0.53</v>
       </c>
       <c r="G2" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>92.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>92.7</v>
+        <v>73.8</v>
       </c>
       <c r="K2" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +553,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>1.03</v>
+        <v>0.53</v>
       </c>
       <c r="G3" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>92.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>92.7</v>
+        <v>73.8</v>
       </c>
       <c r="K3" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -599,43 +599,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>0.53</v>
       </c>
       <c r="G4" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>92.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>92.8</v>
+        <v>73.8</v>
       </c>
       <c r="K4" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -645,43 +645,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
         <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>0.53</v>
       </c>
       <c r="G5" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>92.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>92.8</v>
+        <v>73.8</v>
       </c>
       <c r="K5" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -691,141 +691,141 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
         <v>500</v>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>0.53</v>
       </c>
       <c r="G6" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>92.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>92.8</v>
+        <v>73.8</v>
       </c>
       <c r="K6" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>500</v>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
       <c r="G7" t="n">
-        <v>0.24</v>
+        <v>0.09</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>92.3</v>
+        <v>73.8</v>
       </c>
       <c r="J7" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="K7" t="n">
-        <v>92.8</v>
+        <v>73.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>500</v>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
       <c r="G8" t="n">
-        <v>0.24</v>
+        <v>0.09</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>92.3</v>
+        <v>73.8</v>
       </c>
       <c r="J8" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="K8" t="n">
-        <v>92.8</v>
+        <v>73.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -835,43 +835,43 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>500</v>
       </c>
       <c r="F9" t="n">
-        <v>1.17</v>
+        <v>0.52</v>
       </c>
       <c r="G9" t="n">
-        <v>0.24</v>
+        <v>0.09</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>92.8</v>
+        <v>73.8</v>
       </c>
       <c r="J9" t="n">
-        <v>92.3</v>
+        <v>74</v>
       </c>
       <c r="K9" t="n">
-        <v>92.8</v>
+        <v>73.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -881,43 +881,43 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
         <v>500</v>
       </c>
       <c r="F10" t="n">
-        <v>1.17</v>
+        <v>0.52</v>
       </c>
       <c r="G10" t="n">
-        <v>0.24</v>
+        <v>0.09</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>92.8</v>
+        <v>73.8</v>
       </c>
       <c r="J10" t="n">
-        <v>92.3</v>
+        <v>74</v>
       </c>
       <c r="K10" t="n">
-        <v>92.8</v>
+        <v>73.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>edd</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -927,37 +927,37 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
         <v>500</v>
       </c>
       <c r="F11" t="n">
-        <v>1.17</v>
+        <v>0.52</v>
       </c>
       <c r="G11" t="n">
-        <v>0.24</v>
+        <v>0.09</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>92.8</v>
+        <v>73.8</v>
       </c>
       <c r="J11" t="n">
-        <v>92.3</v>
+        <v>74</v>
       </c>
       <c r="K11" t="n">
-        <v>92.8</v>
+        <v>73.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity_Output/Top10_Configurations.xlsx
+++ b/Sensitivity_Output/Top10_Configurations.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,72 +417,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>avg_travel_hours</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
@@ -528,13 +516,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J2" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -574,13 +562,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J3" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -620,13 +608,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J4" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -666,13 +654,13 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J5" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -712,13 +700,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J6" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -758,13 +746,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="J7" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K7" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -804,13 +792,13 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="J8" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K8" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -850,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="J9" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K9" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -896,13 +884,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="J10" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K10" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -942,13 +930,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="J11" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K11" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Sensitivity_Output/Top10_Configurations.xlsx
+++ b/Sensitivity_Output/Top10_Configurations.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>avg_travel_hours</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
